--- a/docs/EVFTA_eu_Backlog_MVP_bosung_trust.xlsx
+++ b/docs/EVFTA_eu_Backlog_MVP_bosung_trust.xlsx
@@ -12,10 +12,11 @@
     <sheet name="Tổng hợp" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Backlog" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Mô hình dữ liệu" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Lịch tuần" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Ma trận nguồn" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Lịch tuần" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Backlog!$A$1:$P$61</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Backlog!$A$1:$P$67</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1135" uniqueCount="679">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="792">
   <si>
     <t xml:space="preserve">evfta.eu — Backlog MVP xây mới trên FastAPI</t>
   </si>
@@ -110,10 +111,10 @@
     <t xml:space="preserve">Khi trễ: giữ P0, cắt P1 trước. Không làm P2. Yêu cầu P2 từ pilot trả lời 'đưa vào lộ trình seed'.</t>
   </si>
   <si>
-    <t xml:space="preserve">Bổ sung 29/9 (chờ duyệt)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thêm I8 kiểm chéo nguồn cấp (P0, GĐ3), I9 tín hiệu chỉnh sửa file (P1, GĐ4), E5 Trust Profile từng dòng xác nhận (P0, GĐ5). Dòng tô vàng ở Backlog, Mô hình dữ liệu, Lịch tuần. I9 cần duyệt 4 dependency mới. Duyệt xong thì bỏ tô vàng và chữ 'chờ duyệt'.</t>
+    <t xml:space="preserve">Bổ sung 30/9 (chờ duyệt)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theo TRUST_ANTI_FRAUD_FRAMEWORK.md: thêm I11 (GĐ2), I8 + I10 (GĐ3), I9 P1 + E6 (GĐ4), E5 (GĐ5), F4 + B6 P1 (GĐ6), X9 (sau MVP) và sheet 'Ma trận nguồn'. Dòng tô vàng ở Backlog, Mô hình dữ liệu, Lịch tuần. Duyệt xong thì bỏ tô vàng và chữ 'chờ duyệt'.</t>
   </si>
   <si>
     <t xml:space="preserve">Giả định năng lực (sửa ô chữ xanh)</t>
@@ -737,6 +738,27 @@
     <t xml:space="preserve">VYBE C4</t>
   </si>
   <si>
+    <t xml:space="preserve">I11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§5.1 · §5.10 · §6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chống mạo danh và gian lận danh tính</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bảng identity_signals, account_clusters, blocklist_identifiers. Chứng minh quyền sở hữu: admin gọi lại số điện thoại ghi trên hồ sơ đăng ký chính thức (không gọi số seller khai) và ghi kết quả; xác minh email thuộc domain chính thức. Tín hiệu tự động: tuổi domain, email miễn phí cho công ty, công ty thành lập &lt; 1 năm nhưng khai lâu năm, vừa đổi tên/người đại diện, trạng thái thuế không hoạt động. Gom cụm tài khoản dùng chung điện thoại, domain, hash file, người đại diện, thiết bị. Danh sách chặn MST/domain/điện thoại/hash file, kiểm khi đăng ký và khi nộp bằng chứng. Số/IP nước ngoài không tự động là cờ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không đạt 'đã chứng minh quyền sở hữu' thì không lên được evfta_verified; 5/5 ca thử gom cụm đúng (dùng chung điện thoại, domain, hash, người đại diện, thiết bị); định danh trong danh sách chặn không đăng ký lại được; tín hiệu chỉ đẩy lên hàng đợi, không tự từ chối.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B1, I6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MỚI 29/9 — chờ duyệt. Xem TRUST_ANTI_FRAUD_FRAMEWORK.md. Chống kiểu gian lận nguy hiểm nhất: dùng MST và chứng nhận thật của công ty khác.</t>
+  </si>
+  <si>
     <t xml:space="preserve">I7</t>
   </si>
   <si>
@@ -917,7 +939,28 @@
     <t xml:space="preserve">C6, I1, I6</t>
   </si>
   <si>
-    <t xml:space="preserve">MỚI 29/9 — chờ duyệt. VYBE SAS §5.3 bước ② ③ (Cross-source, Duplicate) — làm bằng quy tắc thay vì LLM. Luật TM xác nhận nguồn tra cứu cho ISO, GlobalG.A.P., BRCGS, hữu cơ EU, HACCP.</t>
+    <t xml:space="preserve">MỚI 29/9 — chờ duyệt. Xem TRUST_ANTI_FRAUD_FRAMEWORK.md. VYBE SAS §5.3 bước ② ③ (Cross-source, Duplicate) — làm bằng quy tắc thay vì LLM. Luật TM xác nhận nguồn tra cứu cho ISO, GlobalG.A.P., BRCGS, hữu cơ EU, HACCP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§5.2 · §5.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ma trận nguồn theo nhóm hàng + danh sách tham chiếu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bảng claim_types, category_claim_rules (nhóm hàng → tuyên bố bắt buộc/tăng điểm, thị trường), sources (loại A/B/C/D, URL, phạm vi, tần suất cập nhật, reviewed_by), reference_lists + reference_list_entries (có phiên bản, ngày nhập). Màn hình admin nhập danh sách loại B từ CSV/Excel; so khớp tự động theo MST → mã cơ sở/số chứng nhận → tên + địa chỉ chuẩn hoá (pg_trgm), khớp gần đúng cần admin xác nhận. Nhập đợt đầu 1–2 danh sách giá trị cao nhất (ưu tiên danh sách cơ sở thủy sản EU phê duyệt). Job kiểm lại định kỳ khi có phiên bản danh sách mới.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ma trận nguồn cho nhóm hàng SIAL đã được luật TM duyệt; 1 danh sách loại B nhập được và tự khớp đúng trên dữ liệu thử; khớp gần đúng không bao giờ tự nhận; checklist I8 lấy tuyên bố bắt buộc từ category_claim_rules, không viết cứng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I8, B4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MỚI 29/9 — chờ duyệt. Xem TRUST_ANTI_FRAUD_FRAMEWORK.md. BA soạn sheet Ma trận nguồn, luật TM duyệt.</t>
   </si>
   <si>
     <t xml:space="preserve">D1</t>
@@ -1028,7 +1071,25 @@
     <t xml:space="preserve">C6, I8</t>
   </si>
   <si>
-    <t xml:space="preserve">MỚI 29/9 — chờ duyệt. VYBE SAS §5.3 bước ① ③. Không dùng OCR/AI (X8 vẫn sau MVP). Cần duyệt thêm dependency: pyHanko, pikepdf, imagehash, thư viện đọc QR. P1 — cắt được nếu trễ.</t>
+    <t xml:space="preserve">MỚI 29/9 — chờ duyệt. Xem TRUST_ANTI_FRAUD_FRAMEWORK.md. VYBE SAS §5.3 bước ① ③. Không dùng OCR/AI (X8 vẫn sau MVP). Cần duyệt thêm dependency: pyHanko, pikepdf, imagehash, thư viện đọc QR. P1 — cắt được nếu trễ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§5.2 · §5.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lịch sử thương mại + nhãn nhà xuất khẩu mới</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bảng trade_records (loại: kênh trong nước có kiểm soát chất lượng / xuất khẩu gián tiếp / xuất ngoài EU / xuất EU; chứng từ; đối tác; trạng thái xác nhận) + companies.trade_history_level. Kiểm chứng từ: chữ số kiểm tra container ISO 6346, số vận đơn + link tra cứu hãng tàu, tên người gửi hàng = tên pháp nhân. Xác nhận buyer cũ: đối tác EU phải có VAT hợp lệ trên VIES, admin tìm liên hệ qua website chính thức, gửi bảng hỏi ngắn. 'Sẵn sàng xuất khẩu' lấy từ dữ liệu nền tảng (RoO Đạt, EUR.1 nháp, đủ tuyên bố bắt buộc). Nhãn 'Nhà xuất khẩu mới' khi chưa có trade_record.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số container sai chữ số kiểm tra bị chặn (test); mỗi mức lịch sử có ít nhất 1 bằng chứng đã kiểm; buyer cũ chỉ được tính khi VAT hợp lệ và liên hệ do admin tự tìm; seller chưa xuất khẩu vẫn đạt được Danh tính và Năng lực đầy đủ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MỚI 29/9 — chờ duyệt. Xem TRUST_ANTI_FRAUD_FRAMEWORK.md. Thang lịch sử thương mại độc lập, không phạt seller mới.</t>
   </si>
   <si>
     <t xml:space="preserve">E1</t>
@@ -1115,16 +1176,16 @@
     <t xml:space="preserve">Trust Profile công khai theo từng dòng xác nhận</t>
   </si>
   <si>
-    <t xml:space="preserve">Hồ sơ công khai hiện mỗi dòng: thông tin (pháp nhân, MST + trạng thái, từng chứng nhận), kết quả, nguồn đối chiếu, ngày kiểm, vai trò người duyệt, link tra cứu chính thức để buyer tự kiểm. Ba mức hiển thị: 'Đã xác nhận với nơi cấp' / 'Tài liệu điện tử chưa bị sửa' / 'Đã xem tài liệu, chưa xác nhận nguồn'; bằng chứng còn cờ chưa xử lý thì không hiện. Không công khai file gốc, chỉ trường đã trích; buyer gửi yêu cầu xem file → seller đồng ý → pre-signed URL ngắn hạn, ghi audit (bảng document_access_requests). Câu miễn trừ từ E4 cạnh huy hiệu.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buyer thấy nguồn + ngày kiểm cho mọi dòng; MST có link tra cứu chính thức; file gốc không mở được khi seller chưa đồng ý (test); mọi lượt mở file có nhật ký.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I8, E3, E4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MỚI 29/9 — chờ duyệt. Thay 1 huy hiệu tổng bằng từng dòng xác nhận có nguồn.</t>
+    <t xml:space="preserve">Hồ sơ công khai hiện 4 trục tin cậy độc lập: Danh tính, Năng lực, Lịch sử thương mại, Toàn vẹn. Bấm vào trục thấy từng tuyên bố: kết quả, nguồn đối chiếu, ngày kiểm, vai trò người duyệt, link tra cứu chính thức. Ba nhãn độ mạnh: 'Đã xác nhận với nơi cấp' / 'Tài liệu điện tử chưa bị sửa' / 'Đã xem tài liệu, chưa xác nhận nguồn'; tuyên bố còn cờ chưa xử lý thì không hiện. Không công khai file gốc; buyer xin xem → seller đồng ý → pre-signed URL ngắn hạn, ghi audit (document_access_requests). Câu miễn trừ từ E4.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buyer thấy 4 trục và nguồn + ngày kiểm cho mọi tuyên bố; MST có link tra cứu chính thức; file gốc không mở được khi seller chưa đồng ý (test); mọi lượt mở file có nhật ký.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I8, I10, I11, E6, E3, E4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MỚI 29/9 — chờ duyệt. Xem TRUST_ANTI_FRAUD_FRAMEWORK.md. Thay 1 huy hiệu tổng bằng 4 trục và từng tuyên bố có nguồn.</t>
   </si>
   <si>
     <t xml:space="preserve">H1</t>
@@ -1430,6 +1491,48 @@
     <t xml:space="preserve">VYBE J5</t>
   </si>
   <si>
+    <t xml:space="preserve">F4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§5.7 · §6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cảnh báo lừa thanh toán</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quy tắc phát hiện số tài khoản/IBAN hoặc câu yêu cầu chuyển tiền trong tin nhắn → banner cảnh báo cho buyer ('Luôn xác nhận thông tin thanh toán qua kênh độc lập'); không chặn tin nhắn. Loại bằng chứng 'thư xác nhận ngân hàng' (tài khoản đứng tên pháp nhân); bảng payment_detail_changes, đổi thông tin ngân hàng → cảnh báo nổi bật 30 ngày trên hồ sơ và trong chat. Điều khoản ghi rõ việc quét tìm thông tin thanh toán (luật sư duyệt).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/5 mẫu tin nhắn có thông tin thanh toán hiện cảnh báo, tin nhắn thường không bị báo nhầm trên bộ 20 mẫu; đổi thông tin ngân hàng hiện cảnh báo 30 ngày; Điều khoản đã cập nhật.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F2, C6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MỚI 29/9 — chờ duyệt. Xem TRUST_ANTI_FRAUD_FRAMEWORK.md. Không xử lý thanh toán (X2 vẫn P2) — chỉ xác minh và cảnh báo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">§3 · §5.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhà phân phối tại EU liên kết nhà sản xuất VN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cho phép công ty đăng ký tại EU (xác minh qua sổ đăng ký nước đó + VIES + EORI) tạo hồ sơ nhà phân phối hàng Việt. Bảng company_relationships (producer_id, representative_id, relation_type, bằng chứng uỷ quyền, producer_confirmed_at, expires_at). Nhà sản xuất VN đã xác minh bấm xác nhận liên kết từ tài khoản của mình; chưa xác nhận thì chỉ hiện là nhà thương mại độc lập. Hồ sơ hiện 'Sản xuất bởi … · Phân phối bởi …, uỷ quyền đến …'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không gắn được tên nhà sản xuất khi nhà sản xuất chưa xác nhận (test); liên kết hết hạn thì tự gỡ; nhà sản xuất thu hồi được liên kết.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B2, I7, I8, E5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MỚI 29/9 — chờ duyệt. Xem TRUST_ANTI_FRAUD_FRAMEWORK.md. Mở rộng phạm vi (spec §3 chỉ định nghĩa exporter là công ty VN) — P1, cắt được. Công ty ở nước thứ ba để sau MVP (X9).</t>
+  </si>
+  <si>
     <t xml:space="preserve">X1</t>
   </si>
   <si>
@@ -1526,6 +1629,18 @@
     <t xml:space="preserve">VYBE X3</t>
   </si>
   <si>
+    <t xml:space="preserve">X9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trust nâng cao để sau MVP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chụp ảnh trong app có GPS + mã dùng một lần; video call kiểm tra xưởng; hợp tác phòng thí nghiệm và hãng giám định; thư xác nhận qua bưu điện; kiểm RASFF tự động; báo cáo tín dụng; phát hiện thổi phồng năng lực; khiếu nại công khai; seller ở nước thứ ba ngoài EU (cần luật TM làm rõ quy tắc vận chuyển, hoá đơn nước thứ ba); ELA/máy dò ảnh AI.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MỚI 29/9 — chờ duyệt. Xem TRUST_ANTI_FRAUD_FRAMEWORK.md. </t>
+  </si>
+  <si>
     <t xml:space="preserve">Thực thể spec</t>
   </si>
   <si>
@@ -1763,22 +1878,247 @@
     <t xml:space="preserve">G1, G3</t>
   </si>
   <si>
-    <t xml:space="preserve">Mới, ngoài spec (29/9)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">certification_bodies, evidence_checks, document_access_requests</t>
-  </si>
-  <si>
-    <t xml:space="preserve">certification_bodies: name, official_domain, lookup_url, accreditation_body, iaf_mla, reviewed_by · evidence_checks: evidence_id, check_type, source, result, snapshot_file, note, checked_by, checked_at · document_access_requests: evidence_id, buyer_company_id, status, decided_at, opened_at</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evidence_checks append-only; certification_bodies là dữ liệu cấu hình có người duyệt; file gốc chỉ mở qua pre-signed URL sau khi seller đồng ý</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I8, I9, E5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">— (VYBE có AiVerificationResult, mục đích khác)</t>
+    <t xml:space="preserve">Mới, ngoài spec (30/9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">certification_bodies, evidence_checks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">certification_bodies: name, official_domain, lookup_url, accreditation_body, iaf_mla, reviewed_by · evidence_checks: evidence_id, check_type, source_id, reference_entry_id, result, snapshot_file, note, checked_by, checked_at</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evidence_checks append-only; certification_bodies là cấu hình có người duyệt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I8, I9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">— (VYBE AiVerificationResult là mục đích khác)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">claim_types, category_claim_rules, sources, reference_lists, reference_list_entries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rule: category_id, claim_type_id, required, market · source: type A/B/C/D, url, coverage, update_frequency, reviewed_by · list: source_id, version, imported_at · entry: tax_id, facility_code, name_norm, address_norm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuyên bố bắt buộc là dữ liệu, không viết cứng; khớp gần đúng cần admin xác nhận</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MarketProfile (tham khảo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">identity_signals, account_clusters, blocklist_identifiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">signal: company_id, type, value, severity, detected_at · cluster: shared_identifier, company_ids · blocklist: identifier_type, value, reason, added_by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tín hiệu chỉ xếp ưu tiên, không đổi trạng thái xác minh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trade_records, document_access_requests</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trade_record: company_id, type, counterparty, documents, container_no, bl_no, confirmation_status · access_request: evidence_id, buyer_company_id, status, decided_at, opened_at</t>
+  </si>
+  <si>
+    <t xml:space="preserve">companies.trade_history_level tính từ trade_records đã xác nhận</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E6, E5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">payment_detail_changes, company_relationships</t>
+  </si>
+  <si>
+    <t xml:space="preserve">payment_change: company_id, changed_at, evidence_id · relationship: producer_id, representative_id, relation_type, evidence_id, producer_confirmed_at, expires_at</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liên kết chỉ hiệu lực khi nhà sản xuất VN xác nhận</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F4, B6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nhóm hàng</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tuyên bố</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bắt buộc / Tăng điểm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nguồn đối chiếu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loại nguồn (A/B/C/D)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link / cách tra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tần suất cập nhật</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BA soạn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luật TM duyệt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ngày duyệt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mọi nhóm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pháp nhân tồn tại, đang hoạt động</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bắt buộc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tra cứu người nộp thuế — Tổng cục Thuế</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://tracuunnt.gdt.gov.vn/tcnnt/mstdn.jsp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mỗi lần duyệt + kiểm lại định kỳ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Có captcha — tra tay, lưu ảnh chụp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Đã chứng minh quyền sở hữu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Số điện thoại trên hồ sơ đăng ký chính thức</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cần BA xác định nguồn chính thức có số liên hệ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mỗi lần duyệt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chứng nhận ISO còn hạn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tăng điểm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IAF CertSearch / trang tra cứu của tổ chức cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.iafcertsearch.org/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kiểm thêm tổ chức cấp có được công nhận</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thủy sản</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cơ sở trong danh sách EU phê duyệt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Danh sách cơ sở được EU phê duyệt cho Việt Nam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cần luật TM chỉ nguồn chính thức phía EU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Theo mỗi lần EU cập nhật</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ưu tiên nhập đợt đầu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IUU / chứng nhận khai thác</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cần xác định</t>
+  </si>
+  <si>
+    <t xml:space="preserve">?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gạo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cơ sở đủ điều kiện ATTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cần xác định cơ quan quản lý và cách tra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giống gạo thơm theo NĐ 103/2020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liên quan cảnh báo ST25 ở C2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cà phê, tiêu, điều</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GlobalG.A.P. / hữu cơ EU / Rainforest</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSDL của từng chương trình</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cần BA xác nhận link từng CSDL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trái cây tươi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mã số vùng trồng, cơ sở đóng gói</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cần xác định danh sách công bố</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thực phẩm chế biến</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hồ sơ công bố sản phẩm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hệ thống tra cứu công bố sản phẩm — Cục ATTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://congbosanpham.vfa.gov.vn/filesAction!toLookUpHomePage.do</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HACCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tổ chức cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email tới địa chỉ chính thức của tổ chức cấp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Không có CSDL tập trung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bản nháp minh hoạ — mọi dòng chưa có tên ở cột "Luật TM duyệt" đều chưa được dùng trong code (AGENTS.md §6.1). BA bổ sung dòng, luật TM duyệt.</t>
   </si>
   <si>
     <t xml:space="preserve">Thời gian</t>
@@ -1850,7 +2190,7 @@
     <t xml:space="preserve">20 dòng thuế đã duyệt</t>
   </si>
   <si>
-    <t xml:space="preserve">C3, J1, C2 (API)</t>
+    <t xml:space="preserve">C3, J1, C2 (API); I11</t>
   </si>
   <si>
     <t xml:space="preserve">C2 (giao diện)</t>
@@ -1862,7 +2202,7 @@
     <t xml:space="preserve">Duyệt C1; D0</t>
   </si>
   <si>
-    <t xml:space="preserve">Chuẩn bị SIAL</t>
+    <t xml:space="preserve">Chuẩn bị SIAL; BA soạn Ma trận nguồn</t>
   </si>
   <si>
     <t xml:space="preserve">Đóng băng 15/10</t>
@@ -1877,10 +2217,10 @@
     <t xml:space="preserve">Máy tính thuế chạy trên staging</t>
   </si>
   <si>
-    <t xml:space="preserve">C2, C4 (bảng quy tắc)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2, C4 (giao diện)</t>
+    <t xml:space="preserve">C2, C4 (bảng quy tắc); I11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2, C4 (giao diện); I11 (màn hình cụm, danh sách chặn)</t>
   </si>
   <si>
     <t xml:space="preserve">Test C2, C4</t>
@@ -1913,7 +2253,7 @@
     <t xml:space="preserve">Test C4 (10 ca)</t>
   </si>
   <si>
-    <t xml:space="preserve">Duyệt C4; D0; Xác nhận nguồn tra cứu I8</t>
+    <t xml:space="preserve">Duyệt C4; D0</t>
   </si>
   <si>
     <t xml:space="preserve">Chỉ sửa lỗi</t>
@@ -1925,10 +2265,10 @@
     <t xml:space="preserve">Đủ 50 mã; duyệt hồ sơ dưới 5 phút</t>
   </si>
   <si>
-    <t xml:space="preserve">C5, I2, H2, I4, I5; I8 (checklist)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I2, I4, I5; I8 (màn hình duyệt)</t>
+    <t xml:space="preserve">C5, I2, H2, I4, I5; I8 (checklist); I10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I2, I4, I5; I8, I10 (màn hình duyệt, nhập danh sách)</t>
   </si>
   <si>
     <t xml:space="preserve">D1 cắt đoạn + nhúng</t>
@@ -1937,7 +2277,7 @@
     <t xml:space="preserve">Test C5, I2</t>
   </si>
   <si>
-    <t xml:space="preserve">Duyệt 50 mã; soạn 50 câu</t>
+    <t xml:space="preserve">Duyệt 50 mã; soạn 50 câu; Duyệt Ma trận nguồn I10; xác nhận nguồn I8</t>
   </si>
   <si>
     <t xml:space="preserve">10/11–16/11</t>
@@ -1967,10 +2307,10 @@
     <t xml:space="preserve">Bộ 50 câu đạt ngưỡng luật TM ký</t>
   </si>
   <si>
-    <t xml:space="preserve">D3, I5 (chỉ số AI)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D3 (màn hình admin)</t>
+    <t xml:space="preserve">D3, I5 (chỉ số AI); E6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D3 (màn hình admin); E6</t>
   </si>
   <si>
     <t xml:space="preserve">D2 sửa theo kết quả</t>
@@ -1991,7 +2331,7 @@
     <t xml:space="preserve">E1, E2, F1, H1; E5</t>
   </si>
   <si>
-    <t xml:space="preserve">E2, E3, E4, F1, H1; E5</t>
+    <t xml:space="preserve">E2, E3, E4, F1, H1; E5 (4 trục)</t>
   </si>
   <si>
     <t xml:space="preserve">Theo dõi câu tin cậy thấp</t>
@@ -2033,16 +2373,16 @@
     <t xml:space="preserve">Dashboard hai vai trò</t>
   </si>
   <si>
-    <t xml:space="preserve">G1, G2, G3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G1, G2, J3, A3 (rà chuỗi)</t>
+    <t xml:space="preserve">G1, G2, G3; F4, B6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G1, G2, J3, A3 (rà chuỗi); F4, B6</t>
   </si>
   <si>
     <t xml:space="preserve">J3 trên 390px</t>
   </si>
   <si>
-    <t xml:space="preserve">Ký pilot</t>
+    <t xml:space="preserve">Ký pilot; Luật sư duyệt Điều khoản F4</t>
   </si>
   <si>
     <t xml:space="preserve">15/12–21/12</t>
@@ -2076,7 +2416,7 @@
     <numFmt numFmtId="166" formatCode="0%"/>
     <numFmt numFmtId="167" formatCode="0.0;[RED]\-0.0;\-"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2139,6 +2479,13 @@
       <i val="true"/>
       <sz val="10"/>
       <color rgb="FF555555"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i val="true"/>
+      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2219,7 +2566,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2305,6 +2652,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2742,7 +3093,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3" t="s">
         <v>27</v>
       </c>
@@ -2949,15 +3300,15 @@
         <v>51</v>
       </c>
       <c r="B12" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$J$2:$J$61,A12)</f>
+        <f aca="false">COUNTIFS(Backlog!$J$2:$J$67,A12)</f>
         <v>13</v>
       </c>
       <c r="C12" s="11" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$J$2:$J$61,A12)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$J$2:$J$67,A12)</f>
         <v>24.5</v>
       </c>
       <c r="D12" s="11" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$J$2:$J$61,A12)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$J$2:$J$67,A12)</f>
         <v>6.5</v>
       </c>
       <c r="E12" s="11" t="n">
@@ -2982,15 +3333,15 @@
         <v>52</v>
       </c>
       <c r="B13" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$J$2:$J$61,A13)</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS(Backlog!$J$2:$J$67,A13)</f>
+        <v>6</v>
       </c>
       <c r="C13" s="11" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$J$2:$J$61,A13)</f>
-        <v>11</v>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$J$2:$J$67,A13)</f>
+        <v>14</v>
       </c>
       <c r="D13" s="11" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$J$2:$J$61,A13)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$J$2:$J$67,A13)</f>
         <v>5</v>
       </c>
       <c r="E13" s="11" t="n">
@@ -2999,7 +3350,7 @@
       </c>
       <c r="F13" s="11" t="n">
         <f aca="false">E13-C13*(1+$B$7)</f>
-        <v>14.8</v>
+        <v>11.2</v>
       </c>
       <c r="G13" s="11" t="n">
         <f aca="false">$B$4*$B$6</f>
@@ -3015,16 +3366,16 @@
         <v>53</v>
       </c>
       <c r="B14" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$J$2:$J$61,A14)</f>
-        <v>9</v>
+        <f aca="false">COUNTIFS(Backlog!$J$2:$J$67,A14)</f>
+        <v>10</v>
       </c>
       <c r="C14" s="11" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$J$2:$J$61,A14)</f>
-        <v>20</v>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$J$2:$J$67,A14)</f>
+        <v>22.5</v>
       </c>
       <c r="D14" s="11" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$J$2:$J$61,A14)</f>
-        <v>2</v>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$J$2:$J$67,A14)</f>
+        <v>2.5</v>
       </c>
       <c r="E14" s="11" t="n">
         <f aca="false">$B$3*$B$4*$B$5</f>
@@ -3032,7 +3383,7 @@
       </c>
       <c r="F14" s="11" t="n">
         <f aca="false">E14-C14*(1+$B$7)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G14" s="11" t="n">
         <f aca="false">$B$4*$B$6</f>
@@ -3040,7 +3391,7 @@
       </c>
       <c r="H14" s="11" t="n">
         <f aca="false">G14-D14</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3048,15 +3399,15 @@
         <v>54</v>
       </c>
       <c r="B15" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$J$2:$J$61,A15)</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS(Backlog!$J$2:$J$67,A15)</f>
+        <v>6</v>
       </c>
       <c r="C15" s="11" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$J$2:$J$61,A15)</f>
-        <v>15</v>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$J$2:$J$67,A15)</f>
+        <v>18.5</v>
       </c>
       <c r="D15" s="11" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$J$2:$J$61,A15)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$J$2:$J$67,A15)</f>
         <v>3</v>
       </c>
       <c r="E15" s="11" t="n">
@@ -3065,7 +3416,7 @@
       </c>
       <c r="F15" s="11" t="n">
         <f aca="false">E15-C15*(1+$B$7)</f>
-        <v>10</v>
+        <v>5.8</v>
       </c>
       <c r="G15" s="11" t="n">
         <f aca="false">$B$4*$B$6</f>
@@ -3081,15 +3432,15 @@
         <v>55</v>
       </c>
       <c r="B16" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$J$2:$J$61,A16)</f>
+        <f aca="false">COUNTIFS(Backlog!$J$2:$J$67,A16)</f>
         <v>12</v>
       </c>
       <c r="C16" s="11" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$J$2:$J$61,A16)</f>
-        <v>21</v>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$J$2:$J$67,A16)</f>
+        <v>21.5</v>
       </c>
       <c r="D16" s="11" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$J$2:$J$61,A16)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$J$2:$J$67,A16)</f>
         <v>0</v>
       </c>
       <c r="E16" s="11" t="n">
@@ -3098,7 +3449,7 @@
       </c>
       <c r="F16" s="11" t="n">
         <f aca="false">E16-C16*(1+$B$7)</f>
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="G16" s="11" t="n">
         <f aca="false">$B$4*$B$6</f>
@@ -3114,15 +3465,15 @@
         <v>56</v>
       </c>
       <c r="B17" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$J$2:$J$61,A17)</f>
-        <v>8</v>
+        <f aca="false">COUNTIFS(Backlog!$J$2:$J$67,A17)</f>
+        <v>10</v>
       </c>
       <c r="C17" s="11" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$J$2:$J$61,A17)</f>
-        <v>14</v>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$J$2:$J$67,A17)</f>
+        <v>18.5</v>
       </c>
       <c r="D17" s="11" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$J$2:$J$61,A17)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$J$2:$J$67,A17)</f>
         <v>0</v>
       </c>
       <c r="E17" s="11" t="n">
@@ -3131,7 +3482,7 @@
       </c>
       <c r="F17" s="11" t="n">
         <f aca="false">E17-C17*(1+$B$7)</f>
-        <v>11.2</v>
+        <v>5.8</v>
       </c>
       <c r="G17" s="11" t="n">
         <f aca="false">$B$4*$B$6</f>
@@ -3147,15 +3498,15 @@
         <v>57</v>
       </c>
       <c r="B18" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$J$2:$J$61,A18)</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Backlog!$J$2:$J$67,A18)</f>
+        <v>2</v>
       </c>
       <c r="C18" s="11" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$J$2:$J$61,A18)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$J$2:$J$67,A18)</f>
         <v>0</v>
       </c>
       <c r="D18" s="11" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$J$2:$J$61,A18)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$J$2:$J$67,A18)</f>
         <v>0</v>
       </c>
       <c r="E18" s="11"/>
@@ -3168,15 +3519,15 @@
         <v>58</v>
       </c>
       <c r="B19" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$J$2:$J$61,A19)</f>
+        <f aca="false">COUNTIFS(Backlog!$J$2:$J$67,A19)</f>
         <v>7</v>
       </c>
       <c r="C19" s="11" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$J$2:$J$61,A19)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$J$2:$J$67,A19)</f>
         <v>0</v>
       </c>
       <c r="D19" s="11" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$J$2:$J$61,A19)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$J$2:$J$67,A19)</f>
         <v>0</v>
       </c>
       <c r="E19" s="11"/>
@@ -3190,15 +3541,15 @@
       </c>
       <c r="B20" s="7" t="n">
         <f aca="false">SUM(B12:B19)</f>
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="C20" s="12" t="n">
         <f aca="false">SUM(C12:C19)</f>
-        <v>105.5</v>
+        <v>119.5</v>
       </c>
       <c r="D20" s="12" t="n">
         <f aca="false">SUM(D12:D19)</f>
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="E20" s="12" t="n">
         <f aca="false">SUM(E12:E19)</f>
@@ -3206,7 +3557,7 @@
       </c>
       <c r="F20" s="12" t="n">
         <f aca="false">SUM(F12:F19)</f>
-        <v>41.4</v>
+        <v>24.6</v>
       </c>
       <c r="G20" s="12" t="n">
         <f aca="false">SUM(G12:G19)</f>
@@ -3214,7 +3565,7 @@
       </c>
       <c r="H20" s="12" t="n">
         <f aca="false">SUM(H12:H19)</f>
-        <v>1.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3273,7 +3624,7 @@
       </c>
       <c r="B25" s="11" t="n">
         <f aca="false">C20*(1+B7)</f>
-        <v>126.6</v>
+        <v>143.4</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>63</v>
@@ -3305,7 +3656,7 @@
       </c>
       <c r="B27" s="11" t="n">
         <f aca="false">B26-B25</f>
-        <v>41.4</v>
+        <v>24.6</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="5"/>
@@ -3335,7 +3686,7 @@
       </c>
       <c r="B29" s="11" t="n">
         <f aca="false">D20</f>
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -3421,16 +3772,16 @@
         <v>73</v>
       </c>
       <c r="B35" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$C$2:$C$61,A35)</f>
-        <v>49</v>
+        <f aca="false">COUNTIFS(Backlog!$C$2:$C$67,A35)</f>
+        <v>53</v>
       </c>
       <c r="C35" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$C$2:$C$61,A35)</f>
-        <v>100</v>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$C$2:$C$67,A35)</f>
+        <v>111</v>
       </c>
       <c r="D35" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$C$2:$C$61,A35)</f>
-        <v>16.5</v>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$C$2:$C$67,A35)</f>
+        <v>17</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -3442,15 +3793,15 @@
         <v>74</v>
       </c>
       <c r="B36" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$C$2:$C$61,A36)</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Backlog!$C$2:$C$67,A36)</f>
+        <v>4</v>
       </c>
       <c r="C36" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$C$2:$C$61,A36)</f>
-        <v>5.5</v>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$C$2:$C$67,A36)</f>
+        <v>8.5</v>
       </c>
       <c r="D36" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$C$2:$C$61,A36)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$C$2:$C$67,A36)</f>
         <v>0</v>
       </c>
       <c r="E36" s="5"/>
@@ -3463,15 +3814,15 @@
         <v>75</v>
       </c>
       <c r="B37" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$C$2:$C$61,A37)</f>
+        <f aca="false">COUNTIFS(Backlog!$C$2:$C$67,A37)</f>
         <v>7</v>
       </c>
       <c r="C37" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$C$2:$C$61,A37)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$C$2:$C$67,A37)</f>
         <v>0</v>
       </c>
       <c r="D37" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$C$2:$C$61,A37)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$C$2:$C$67,A37)</f>
         <v>0</v>
       </c>
       <c r="E37" s="5"/>
@@ -3484,15 +3835,15 @@
         <v>76</v>
       </c>
       <c r="B38" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$C$2:$C$61,A38)</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Backlog!$C$2:$C$67,A38)</f>
+        <v>2</v>
       </c>
       <c r="C38" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$C$2:$C$61,A38)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$C$2:$C$67,A38)</f>
         <v>0</v>
       </c>
       <c r="D38" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$C$2:$C$61,A38)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$C$2:$C$67,A38)</f>
         <v>0</v>
       </c>
       <c r="E38" s="5"/>
@@ -3545,15 +3896,15 @@
         <v>79</v>
       </c>
       <c r="B42" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$D$2:$D$61,A42)</f>
+        <f aca="false">COUNTIFS(Backlog!$D$2:$D$67,A42)</f>
         <v>2</v>
       </c>
       <c r="C42" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$D$2:$D$61,A42)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$D$2:$D$67,A42)</f>
         <v>7</v>
       </c>
       <c r="D42" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$D$2:$D$61,A42)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$D$2:$D$67,A42)</f>
         <v>0</v>
       </c>
       <c r="E42" s="5"/>
@@ -3566,16 +3917,16 @@
         <v>80</v>
       </c>
       <c r="B43" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$D$2:$D$61,A43)</f>
-        <v>8</v>
+        <f aca="false">COUNTIFS(Backlog!$D$2:$D$67,A43)</f>
+        <v>10</v>
       </c>
       <c r="C43" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$D$2:$D$61,A43)</f>
-        <v>17</v>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$D$2:$D$67,A43)</f>
+        <v>22.5</v>
       </c>
       <c r="D43" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$D$2:$D$61,A43)</f>
-        <v>0.5</v>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$D$2:$D$67,A43)</f>
+        <v>1</v>
       </c>
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
@@ -3587,15 +3938,15 @@
         <v>81</v>
       </c>
       <c r="B44" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$D$2:$D$61,A44)</f>
+        <f aca="false">COUNTIFS(Backlog!$D$2:$D$67,A44)</f>
         <v>3</v>
       </c>
       <c r="C44" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$D$2:$D$61,A44)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$D$2:$D$67,A44)</f>
         <v>7</v>
       </c>
       <c r="D44" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$D$2:$D$61,A44)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$D$2:$D$67,A44)</f>
         <v>0</v>
       </c>
       <c r="E44" s="5"/>
@@ -3608,15 +3959,15 @@
         <v>82</v>
       </c>
       <c r="B45" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$D$2:$D$61,A45)</f>
-        <v>5</v>
+        <f aca="false">COUNTIFS(Backlog!$D$2:$D$67,A45)</f>
+        <v>7</v>
       </c>
       <c r="C45" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$D$2:$D$61,A45)</f>
-        <v>9</v>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$D$2:$D$67,A45)</f>
+        <v>15.5</v>
       </c>
       <c r="D45" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$D$2:$D$61,A45)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$D$2:$D$67,A45)</f>
         <v>0.5</v>
       </c>
       <c r="E45" s="5"/>
@@ -3629,15 +3980,15 @@
         <v>83</v>
       </c>
       <c r="B46" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$D$2:$D$61,A46)</f>
+        <f aca="false">COUNTIFS(Backlog!$D$2:$D$67,A46)</f>
         <v>7</v>
       </c>
       <c r="C46" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$D$2:$D$61,A46)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$D$2:$D$67,A46)</f>
         <v>15.5</v>
       </c>
       <c r="D46" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$D$2:$D$61,A46)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$D$2:$D$67,A46)</f>
         <v>7.5</v>
       </c>
       <c r="E46" s="5"/>
@@ -3650,15 +4001,15 @@
         <v>84</v>
       </c>
       <c r="B47" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$D$2:$D$61,A47)</f>
+        <f aca="false">COUNTIFS(Backlog!$D$2:$D$67,A47)</f>
         <v>5</v>
       </c>
       <c r="C47" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$D$2:$D$61,A47)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$D$2:$D$67,A47)</f>
         <v>12</v>
       </c>
       <c r="D47" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$D$2:$D$61,A47)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$D$2:$D$67,A47)</f>
         <v>8</v>
       </c>
       <c r="E47" s="5"/>
@@ -3671,15 +4022,15 @@
         <v>85</v>
       </c>
       <c r="B48" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$D$2:$D$61,A48)</f>
+        <f aca="false">COUNTIFS(Backlog!$D$2:$D$67,A48)</f>
         <v>5</v>
       </c>
       <c r="C48" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$D$2:$D$61,A48)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$D$2:$D$67,A48)</f>
         <v>8</v>
       </c>
       <c r="D48" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$D$2:$D$61,A48)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$D$2:$D$67,A48)</f>
         <v>0</v>
       </c>
       <c r="E48" s="5"/>
@@ -3692,15 +4043,15 @@
         <v>86</v>
       </c>
       <c r="B49" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$D$2:$D$61,A49)</f>
+        <f aca="false">COUNTIFS(Backlog!$D$2:$D$67,A49)</f>
         <v>2</v>
       </c>
       <c r="C49" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$D$2:$D$61,A49)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$D$2:$D$67,A49)</f>
         <v>4</v>
       </c>
       <c r="D49" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$D$2:$D$61,A49)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$D$2:$D$67,A49)</f>
         <v>0</v>
       </c>
       <c r="E49" s="5"/>
@@ -3713,15 +4064,15 @@
         <v>87</v>
       </c>
       <c r="B50" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$D$2:$D$61,A50)</f>
+        <f aca="false">COUNTIFS(Backlog!$D$2:$D$67,A50)</f>
         <v>5</v>
       </c>
       <c r="C50" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$D$2:$D$61,A50)</f>
-        <v>7.5</v>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$D$2:$D$67,A50)</f>
+        <v>8</v>
       </c>
       <c r="D50" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$D$2:$D$61,A50)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$D$2:$D$67,A50)</f>
         <v>0</v>
       </c>
       <c r="E50" s="5"/>
@@ -3734,15 +4085,15 @@
         <v>88</v>
       </c>
       <c r="B51" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$D$2:$D$61,A51)</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Backlog!$D$2:$D$67,A51)</f>
+        <v>4</v>
       </c>
       <c r="C51" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$D$2:$D$61,A51)</f>
-        <v>7</v>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$D$2:$D$67,A51)</f>
+        <v>8.5</v>
       </c>
       <c r="D51" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$D$2:$D$61,A51)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$D$2:$D$67,A51)</f>
         <v>0</v>
       </c>
       <c r="E51" s="5"/>
@@ -3755,15 +4106,15 @@
         <v>89</v>
       </c>
       <c r="B52" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$D$2:$D$61,A52)</f>
+        <f aca="false">COUNTIFS(Backlog!$D$2:$D$67,A52)</f>
         <v>2</v>
       </c>
       <c r="C52" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$D$2:$D$61,A52)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$D$2:$D$67,A52)</f>
         <v>2.5</v>
       </c>
       <c r="D52" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$D$2:$D$61,A52)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$D$2:$D$67,A52)</f>
         <v>0</v>
       </c>
       <c r="E52" s="5"/>
@@ -3776,15 +4127,15 @@
         <v>90</v>
       </c>
       <c r="B53" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$D$2:$D$61,A53)</f>
+        <f aca="false">COUNTIFS(Backlog!$D$2:$D$67,A53)</f>
         <v>3</v>
       </c>
       <c r="C53" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$D$2:$D$61,A53)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$D$2:$D$67,A53)</f>
         <v>6</v>
       </c>
       <c r="D53" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$D$2:$D$61,A53)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$D$2:$D$67,A53)</f>
         <v>0</v>
       </c>
       <c r="E53" s="5"/>
@@ -3797,15 +4148,15 @@
         <v>91</v>
       </c>
       <c r="B54" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$D$2:$D$61,A54)</f>
+        <f aca="false">COUNTIFS(Backlog!$D$2:$D$67,A54)</f>
         <v>2</v>
       </c>
       <c r="C54" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$D$2:$D$61,A54)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$D$2:$D$67,A54)</f>
         <v>3</v>
       </c>
       <c r="D54" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$D$2:$D$61,A54)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$D$2:$D$67,A54)</f>
         <v>0</v>
       </c>
       <c r="E54" s="5"/>
@@ -3818,15 +4169,15 @@
         <v>92</v>
       </c>
       <c r="B55" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$D$2:$D$61,A55)</f>
-        <v>8</v>
+        <f aca="false">COUNTIFS(Backlog!$D$2:$D$67,A55)</f>
+        <v>9</v>
       </c>
       <c r="C55" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$D$2:$D$61,A55)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$D$2:$D$67,A55)</f>
         <v>0</v>
       </c>
       <c r="D55" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$I$2:$I$61,Backlog!$D$2:$D$61,A55)</f>
+        <f aca="false">SUMIFS(Backlog!$I$2:$I$67,Backlog!$D$2:$D$67,A55)</f>
         <v>0</v>
       </c>
       <c r="E55" s="5"/>
@@ -3879,16 +4230,16 @@
         <v>95</v>
       </c>
       <c r="B59" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$O$2:$O$61,A59)</f>
-        <v>52</v>
+        <f aca="false">COUNTIFS(Backlog!$O$2:$O$67,A59)</f>
+        <v>57</v>
       </c>
       <c r="C59" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$O$2:$O$61,A59)</f>
-        <v>105.5</v>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$O$2:$O$67,A59)</f>
+        <v>119.5</v>
       </c>
       <c r="D59" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$O$2:$O$61,A59,Backlog!$C$2:$C$61,"P0")</f>
-        <v>49</v>
+        <f aca="false">COUNTIFS(Backlog!$O$2:$O$67,A59,Backlog!$C$2:$C$67,"P0")</f>
+        <v>53</v>
       </c>
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
@@ -3900,15 +4251,15 @@
         <v>96</v>
       </c>
       <c r="B60" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$O$2:$O$61,A60)</f>
+        <f aca="false">COUNTIFS(Backlog!$O$2:$O$67,A60)</f>
         <v>0</v>
       </c>
       <c r="C60" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$O$2:$O$61,A60)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$O$2:$O$67,A60)</f>
         <v>0</v>
       </c>
       <c r="D60" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$O$2:$O$61,A60,Backlog!$C$2:$C$61,"P0")</f>
+        <f aca="false">COUNTIFS(Backlog!$O$2:$O$67,A60,Backlog!$C$2:$C$67,"P0")</f>
         <v>0</v>
       </c>
       <c r="E60" s="5"/>
@@ -3921,15 +4272,15 @@
         <v>97</v>
       </c>
       <c r="B61" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$O$2:$O$61,A61)</f>
+        <f aca="false">COUNTIFS(Backlog!$O$2:$O$67,A61)</f>
         <v>0</v>
       </c>
       <c r="C61" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$O$2:$O$61,A61)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$O$2:$O$67,A61)</f>
         <v>0</v>
       </c>
       <c r="D61" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$O$2:$O$61,A61,Backlog!$C$2:$C$61,"P0")</f>
+        <f aca="false">COUNTIFS(Backlog!$O$2:$O$67,A61,Backlog!$C$2:$C$67,"P0")</f>
         <v>0</v>
       </c>
       <c r="E61" s="5"/>
@@ -3942,15 +4293,15 @@
         <v>98</v>
       </c>
       <c r="B62" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$O$2:$O$61,A62)</f>
+        <f aca="false">COUNTIFS(Backlog!$O$2:$O$67,A62)</f>
         <v>0</v>
       </c>
       <c r="C62" s="5" t="n">
-        <f aca="false">SUMIFS(Backlog!$H$2:$H$61,Backlog!$O$2:$O$61,A62)</f>
+        <f aca="false">SUMIFS(Backlog!$H$2:$H$67,Backlog!$O$2:$O$67,A62)</f>
         <v>0</v>
       </c>
       <c r="D62" s="5" t="n">
-        <f aca="false">COUNTIFS(Backlog!$O$2:$O$61,A62,Backlog!$C$2:$C$61,"P0")</f>
+        <f aca="false">COUNTIFS(Backlog!$O$2:$O$67,A62,Backlog!$C$2:$C$67,"P0")</f>
         <v>0</v>
       </c>
       <c r="E62" s="5"/>
@@ -3989,7 +4340,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P61"/>
+  <dimension ref="A1:P67"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
@@ -4924,55 +5275,55 @@
       </c>
       <c r="P19" s="17"/>
     </row>
-    <row r="20" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15" t="s">
+    <row r="20" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="19" t="s">
         <v>240</v>
       </c>
-      <c r="H20" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I20" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K20" s="4" t="s">
+      <c r="H20" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I20" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="K20" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="L20" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="M20" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="L20" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="N20" s="4" t="s">
+      <c r="N20" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="O20" s="4" t="s">
+      <c r="O20" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="P20" s="17"/>
-    </row>
-    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P20" s="21"/>
+    </row>
+    <row r="21" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
         <v>243</v>
       </c>
@@ -4995,7 +5346,7 @@
         <v>247</v>
       </c>
       <c r="H21" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="16" t="n">
         <v>0</v>
@@ -5004,103 +5355,103 @@
         <v>53</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>236</v>
+        <v>154</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O21" s="4" t="s">
         <v>95</v>
       </c>
       <c r="P21" s="17"/>
     </row>
-    <row r="22" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>73</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H22" s="16" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I22" s="16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>53</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="L22" s="4" t="s">
         <v>132</v>
       </c>
       <c r="M22" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="N22" s="4" t="s">
         <v>255</v>
-      </c>
-      <c r="N22" s="4" t="s">
-        <v>256</v>
       </c>
       <c r="O22" s="4" t="s">
         <v>95</v>
       </c>
       <c r="P22" s="17"/>
     </row>
-    <row r="23" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>258</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>73</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E23" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F23" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="G23" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>261</v>
       </c>
       <c r="H23" s="16" t="n">
         <v>2.5</v>
       </c>
       <c r="I23" s="16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" s="4" t="s">
         <v>53</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="L23" s="4" t="s">
         <v>132</v>
@@ -5116,7 +5467,7 @@
       </c>
       <c r="P23" s="17"/>
     </row>
-    <row r="24" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="15" t="s">
         <v>264</v>
       </c>
@@ -5127,7 +5478,7 @@
         <v>73</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>266</v>
@@ -5139,70 +5490,70 @@
         <v>268</v>
       </c>
       <c r="H24" s="16" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="I24" s="16" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J24" s="4" t="s">
         <v>53</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>227</v>
+        <v>269</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="O24" s="4" t="s">
         <v>95</v>
       </c>
       <c r="P24" s="17"/>
     </row>
-    <row r="25" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="15" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>73</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H25" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I25" s="16" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J25" s="4" t="s">
         <v>53</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="L25" s="4" t="s">
         <v>116</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>110</v>
+        <v>227</v>
       </c>
       <c r="N25" s="4" t="s">
         <v>276</v>
@@ -5212,30 +5563,30 @@
       </c>
       <c r="P25" s="17"/>
     </row>
-    <row r="26" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="15" t="s">
         <v>277</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>258</v>
+        <v>278</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>73</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H26" s="16" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="I26" s="16" t="n">
         <v>0</v>
@@ -5244,16 +5595,16 @@
         <v>53</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="O26" s="4" t="s">
         <v>95</v>
@@ -5262,10 +5613,10 @@
     </row>
     <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>73</v>
@@ -5274,16 +5625,16 @@
         <v>80</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H27" s="16" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="I27" s="16" t="n">
         <v>0</v>
@@ -5292,13 +5643,13 @@
         <v>53</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="L27" s="4" t="s">
         <v>132</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>288</v>
+        <v>126</v>
       </c>
       <c r="N27" s="4" t="s">
         <v>289</v>
@@ -5308,156 +5659,156 @@
       </c>
       <c r="P27" s="17"/>
     </row>
-    <row r="28" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
+    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="F28" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="H28" s="16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="L28" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="M28" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="P28" s="17"/>
+    </row>
+    <row r="29" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="B29" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="C29" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="D29" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="E28" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="G28" s="19" t="s">
-        <v>294</v>
-      </c>
-      <c r="H28" s="20" t="n">
+      <c r="E29" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="F29" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="G29" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="H29" s="20" t="n">
         <v>3</v>
       </c>
-      <c r="I28" s="20" t="n">
+      <c r="I29" s="20" t="n">
         <v>0.5</v>
       </c>
-      <c r="J28" s="19" t="s">
+      <c r="J29" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="K28" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="L28" s="19" t="s">
+      <c r="K29" s="19" t="s">
+        <v>261</v>
+      </c>
+      <c r="L29" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="M28" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="N28" s="19" t="s">
-        <v>296</v>
-      </c>
-      <c r="O28" s="19" t="s">
+      <c r="M29" s="19" t="s">
+        <v>302</v>
+      </c>
+      <c r="N29" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="O29" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="P28" s="21"/>
-    </row>
-    <row r="29" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="C29" s="4" t="s">
+      <c r="P29" s="21"/>
+    </row>
+    <row r="30" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="B30" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="C30" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="G29" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="H29" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I29" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="M29" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="N29" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="O29" s="4" t="s">
+      <c r="D30" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E30" s="19" t="s">
+        <v>306</v>
+      </c>
+      <c r="F30" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="G30" s="19" t="s">
+        <v>308</v>
+      </c>
+      <c r="H30" s="20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I30" s="20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J30" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="K30" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="L30" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="M30" s="19" t="s">
+        <v>309</v>
+      </c>
+      <c r="N30" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="O30" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="P29" s="17"/>
-    </row>
-    <row r="30" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
-        <v>305</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="H30" s="16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I30" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="L30" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="N30" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="O30" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="P30" s="17"/>
+      <c r="P30" s="21"/>
     </row>
     <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>312</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>306</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>73</v>
@@ -5475,10 +5826,10 @@
         <v>315</v>
       </c>
       <c r="H31" s="16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I31" s="16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J31" s="4" t="s">
         <v>54</v>
@@ -5490,22 +5841,22 @@
         <v>317</v>
       </c>
       <c r="M31" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="N31" s="4" t="s">
         <v>318</v>
-      </c>
-      <c r="N31" s="4" t="s">
-        <v>319</v>
       </c>
       <c r="O31" s="4" t="s">
         <v>95</v>
       </c>
       <c r="P31" s="17"/>
     </row>
-    <row r="32" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>320</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>321</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>73</v>
@@ -5514,13 +5865,13 @@
         <v>84</v>
       </c>
       <c r="E32" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>322</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="G32" s="4" t="s">
         <v>323</v>
-      </c>
-      <c r="G32" s="4" t="s">
-        <v>324</v>
       </c>
       <c r="H32" s="16" t="n">
         <v>1.5</v>
@@ -5532,71 +5883,71 @@
         <v>54</v>
       </c>
       <c r="K32" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>317</v>
+      </c>
+      <c r="M32" s="4" t="s">
+        <v>311</v>
+      </c>
+      <c r="N32" s="4" t="s">
         <v>325</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="N32" s="4" t="s">
-        <v>326</v>
       </c>
       <c r="O32" s="4" t="s">
         <v>95</v>
       </c>
       <c r="P32" s="17"/>
     </row>
-    <row r="33" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="18" t="s">
+    <row r="33" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="15" t="s">
+        <v>326</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>320</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="F33" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="C33" s="19" t="s">
-        <v>74</v>
-      </c>
-      <c r="D33" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="E33" s="19" t="s">
+      <c r="G33" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="F33" s="19" t="s">
+      <c r="H33" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="I33" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="K33" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="G33" s="19" t="s">
+      <c r="L33" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="H33" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="I33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="K33" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="L33" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="M33" s="19" t="s">
+      <c r="M33" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="N33" s="19" t="s">
+      <c r="N33" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="O33" s="19" t="s">
+      <c r="O33" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="P33" s="21"/>
-    </row>
-    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P33" s="17"/>
+    </row>
+    <row r="34" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="15" t="s">
         <v>334</v>
       </c>
@@ -5607,7 +5958,7 @@
         <v>73</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>336</v>
@@ -5619,133 +5970,133 @@
         <v>338</v>
       </c>
       <c r="H34" s="16" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="I34" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>339</v>
       </c>
       <c r="L34" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="M34" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="N34" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="M34" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="N34" s="4" t="s">
-        <v>341</v>
       </c>
       <c r="O34" s="4" t="s">
         <v>95</v>
       </c>
       <c r="P34" s="17"/>
     </row>
-    <row r="35" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15" t="s">
+    <row r="35" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="18" t="s">
+        <v>341</v>
+      </c>
+      <c r="B35" s="19" t="s">
         <v>342</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="E35" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="H35" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I35" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="K35" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="L35" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="M35" s="19" t="s">
+        <v>346</v>
+      </c>
+      <c r="N35" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="O35" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="P35" s="21"/>
+    </row>
+    <row r="36" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="18" t="s">
+        <v>348</v>
+      </c>
+      <c r="B36" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="C36" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D35" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="H35" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I35" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K35" s="4" t="s">
+      <c r="D36" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="G36" s="19" t="s">
+        <v>352</v>
+      </c>
+      <c r="H36" s="20" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I36" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="K36" s="19" t="s">
         <v>339</v>
       </c>
-      <c r="L35" s="4" t="s">
+      <c r="L36" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="M35" s="4" t="s">
+      <c r="M36" s="19" t="s">
         <v>346</v>
       </c>
-      <c r="N35" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="O35" s="4" t="s">
+      <c r="N36" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="O36" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="P35" s="17"/>
-    </row>
-    <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15" t="s">
-        <v>348</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="G36" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="H36" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="I36" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="L36" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="M36" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="N36" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="O36" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="P36" s="17"/>
+      <c r="P36" s="21"/>
     </row>
     <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="15" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>73</v>
@@ -5754,16 +6105,16 @@
         <v>87</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H37" s="16" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="I37" s="16" t="n">
         <v>0</v>
@@ -5772,94 +6123,94 @@
         <v>55</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>124</v>
+        <v>360</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>118</v>
+        <v>243</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="O37" s="4" t="s">
         <v>95</v>
       </c>
       <c r="P37" s="17"/>
     </row>
-    <row r="38" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="s">
+    <row r="38" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="15" t="s">
+        <v>362</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>363</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="H38" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="I38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="K38" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="B38" s="19" t="s">
-        <v>360</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>73</v>
-      </c>
-      <c r="D38" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="E38" s="19" t="s">
-        <v>361</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="G38" s="19" t="s">
-        <v>363</v>
-      </c>
-      <c r="H38" s="20" t="n">
-        <v>2</v>
-      </c>
-      <c r="I38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="K38" s="19" t="s">
-        <v>339</v>
-      </c>
-      <c r="L38" s="19" t="s">
+      <c r="L38" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="M38" s="19" t="s">
-        <v>364</v>
-      </c>
-      <c r="N38" s="19" t="s">
-        <v>365</v>
-      </c>
-      <c r="O38" s="19" t="s">
+      <c r="M38" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="O38" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="P38" s="21"/>
+      <c r="P38" s="17"/>
     </row>
     <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="15" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>367</v>
+        <v>355</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>73</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H39" s="16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I39" s="16" t="n">
         <v>0</v>
@@ -5868,46 +6219,46 @@
         <v>55</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>118</v>
+        <v>362</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O39" s="4" t="s">
         <v>95</v>
       </c>
       <c r="P39" s="17"/>
     </row>
-    <row r="40" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="15" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>73</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H40" s="16" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="I40" s="16" t="n">
         <v>0</v>
@@ -5916,94 +6267,94 @@
         <v>55</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>348</v>
+        <v>118</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O40" s="4" t="s">
         <v>95</v>
       </c>
       <c r="P40" s="17"/>
     </row>
-    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15" t="s">
-        <v>378</v>
-      </c>
-      <c r="B41" s="4" t="s">
+    <row r="41" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="18" t="s">
         <v>379</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="B41" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="C41" s="19" t="s">
         <v>73</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="F41" s="4" t="s">
+      <c r="D41" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="E41" s="19" t="s">
         <v>381</v>
       </c>
-      <c r="G41" s="4" t="s">
+      <c r="F41" s="19" t="s">
         <v>382</v>
       </c>
-      <c r="H41" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="I41" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="4" t="s">
+      <c r="G41" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="H41" s="20" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="K41" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="L41" s="4" t="s">
+      <c r="K41" s="19" t="s">
+        <v>359</v>
+      </c>
+      <c r="L41" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="M41" s="4" t="s">
-        <v>372</v>
-      </c>
-      <c r="N41" s="4" t="s">
+      <c r="M41" s="19" t="s">
         <v>384</v>
       </c>
-      <c r="O41" s="4" t="s">
+      <c r="N41" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="O41" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="P41" s="17"/>
-    </row>
-    <row r="42" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P41" s="21"/>
+    </row>
+    <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="15" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>373</v>
+        <v>387</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>73</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H42" s="16" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="I42" s="16" t="n">
         <v>0</v>
@@ -6012,46 +6363,46 @@
         <v>55</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>389</v>
+        <v>118</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O42" s="4" t="s">
         <v>95</v>
       </c>
       <c r="P42" s="17"/>
     </row>
-    <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="15" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H43" s="16" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="I43" s="16" t="n">
         <v>0</v>
@@ -6060,16 +6411,16 @@
         <v>55</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>383</v>
+        <v>359</v>
       </c>
       <c r="L43" s="4" t="s">
         <v>132</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>342</v>
+        <v>368</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="O43" s="4" t="s">
         <v>95</v>
@@ -6078,28 +6429,28 @@
     </row>
     <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="15" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H44" s="16" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="I44" s="16" t="n">
         <v>0</v>
@@ -6108,16 +6459,16 @@
         <v>55</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="O44" s="4" t="s">
         <v>95</v>
@@ -6126,28 +6477,28 @@
     </row>
     <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="15" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>354</v>
+        <v>393</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>73</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H45" s="16" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I45" s="16" t="n">
         <v>0</v>
@@ -6156,82 +6507,82 @@
         <v>55</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>116</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O45" s="4" t="s">
         <v>95</v>
       </c>
       <c r="P45" s="17"/>
     </row>
-    <row r="46" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="15" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H46" s="16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I46" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="L46" s="4" t="s">
         <v>132</v>
       </c>
       <c r="M46" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="N46" s="4" t="s">
         <v>416</v>
-      </c>
-      <c r="N46" s="4" t="s">
-        <v>417</v>
       </c>
       <c r="O46" s="4" t="s">
         <v>95</v>
       </c>
       <c r="P46" s="17"/>
     </row>
-    <row r="47" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="15" t="s">
+        <v>417</v>
+      </c>
+      <c r="B47" s="4" t="s">
         <v>418</v>
       </c>
-      <c r="B47" s="4" t="s">
-        <v>411</v>
-      </c>
       <c r="C47" s="4" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>419</v>
@@ -6243,19 +6594,19 @@
         <v>421</v>
       </c>
       <c r="H47" s="16" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="I47" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="M47" s="4" t="s">
         <v>422</v>
@@ -6268,18 +6619,18 @@
       </c>
       <c r="P47" s="17"/>
     </row>
-    <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="15" t="s">
         <v>424</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>411</v>
+        <v>374</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>73</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>425</v>
@@ -6291,16 +6642,16 @@
         <v>427</v>
       </c>
       <c r="H48" s="16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I48" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>415</v>
+        <v>403</v>
       </c>
       <c r="L48" s="4" t="s">
         <v>116</v>
@@ -6316,30 +6667,30 @@
       </c>
       <c r="P48" s="17"/>
     </row>
-    <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="15" t="s">
         <v>430</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>354</v>
+        <v>431</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>73</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H49" s="16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I49" s="16" t="n">
         <v>0</v>
@@ -6348,16 +6699,16 @@
         <v>56</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>434</v>
+        <v>132</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O49" s="4" t="s">
         <v>95</v>
@@ -6366,16 +6717,16 @@
     </row>
     <row r="50" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="15" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>73</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>439</v>
@@ -6387,7 +6738,7 @@
         <v>441</v>
       </c>
       <c r="H50" s="16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I50" s="16" t="n">
         <v>0</v>
@@ -6396,16 +6747,16 @@
         <v>56</v>
       </c>
       <c r="K50" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="L50" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="M50" s="4" t="s">
         <v>442</v>
       </c>
-      <c r="L50" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="M50" s="4" t="s">
+      <c r="N50" s="4" t="s">
         <v>443</v>
-      </c>
-      <c r="N50" s="4" t="s">
-        <v>444</v>
       </c>
       <c r="O50" s="4" t="s">
         <v>95</v>
@@ -6414,25 +6765,25 @@
     </row>
     <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="15" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>354</v>
+        <v>431</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>73</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="E51" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="F51" s="4" t="s">
         <v>446</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="G51" s="4" t="s">
         <v>447</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>448</v>
       </c>
       <c r="H51" s="16" t="n">
         <v>1</v>
@@ -6444,16 +6795,16 @@
         <v>56</v>
       </c>
       <c r="K51" s="4" t="s">
+        <v>435</v>
+      </c>
+      <c r="L51" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M51" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="N51" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="L51" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="M51" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="N51" s="4" t="s">
-        <v>452</v>
       </c>
       <c r="O51" s="4" t="s">
         <v>95</v>
@@ -6462,10 +6813,10 @@
     </row>
     <row r="52" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="15" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>454</v>
+        <v>374</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>73</v>
@@ -6474,13 +6825,13 @@
         <v>85</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="H52" s="16" t="n">
         <v>2</v>
@@ -6492,28 +6843,28 @@
         <v>56</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>449</v>
+        <v>435</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>340</v>
+        <v>454</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>76</v>
+        <v>455</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>311</v>
+        <v>456</v>
       </c>
       <c r="O52" s="4" t="s">
         <v>95</v>
       </c>
       <c r="P52" s="17"/>
     </row>
-    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>458</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>459</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>73</v>
@@ -6522,16 +6873,16 @@
         <v>91</v>
       </c>
       <c r="E53" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="F53" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="G53" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="G53" s="4" t="s">
-        <v>462</v>
-      </c>
       <c r="H53" s="16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I53" s="16" t="n">
         <v>0</v>
@@ -6540,16 +6891,16 @@
         <v>56</v>
       </c>
       <c r="K53" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="L53" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="M53" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="L53" s="4" t="s">
+      <c r="N53" s="4" t="s">
         <v>464</v>
-      </c>
-      <c r="M53" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="N53" s="4" t="s">
-        <v>466</v>
       </c>
       <c r="O53" s="4" t="s">
         <v>95</v>
@@ -6558,121 +6909,121 @@
     </row>
     <row r="54" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="15" t="s">
+        <v>465</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E54" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="F54" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="G54" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="C54" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E54" s="4" t="s">
+      <c r="H54" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K54" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="F54" s="4" t="s">
+      <c r="L54" s="4" t="s">
         <v>470</v>
       </c>
-      <c r="G54" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H54" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K54" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="L54" s="4" t="s">
-        <v>76</v>
-      </c>
       <c r="M54" s="4" t="s">
-        <v>76</v>
+        <v>471</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="P54" s="17"/>
     </row>
     <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="15" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>76</v>
+        <v>477</v>
       </c>
       <c r="H55" s="16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I55" s="16" t="n">
         <v>0</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>76</v>
+        <v>469</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>76</v>
+        <v>360</v>
       </c>
       <c r="M55" s="4" t="s">
         <v>76</v>
       </c>
       <c r="N55" s="4" t="s">
-        <v>475</v>
+        <v>325</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="P55" s="17"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="15" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>76</v>
+        <v>482</v>
       </c>
       <c r="H56" s="16" t="n">
         <v>0</v>
@@ -6681,127 +7032,127 @@
         <v>0</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>76</v>
+        <v>483</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>76</v>
+        <v>484</v>
       </c>
       <c r="M56" s="4" t="s">
-        <v>76</v>
+        <v>485</v>
       </c>
       <c r="N56" s="4" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="P56" s="17"/>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="15" t="s">
-        <v>480</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>482</v>
-      </c>
-      <c r="G57" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H57" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K57" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="L57" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="M57" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="N57" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="O57" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="P57" s="17"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="15" t="s">
-        <v>484</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="E58" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="F58" s="4" t="s">
-        <v>486</v>
-      </c>
-      <c r="G58" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H58" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="K58" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="L58" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="M58" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="N58" s="4" t="s">
+    <row r="57" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="18" t="s">
         <v>487</v>
       </c>
-      <c r="O58" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="P58" s="17"/>
+      <c r="B57" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="D57" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E57" s="19" t="s">
+        <v>489</v>
+      </c>
+      <c r="F57" s="19" t="s">
+        <v>490</v>
+      </c>
+      <c r="G57" s="19" t="s">
+        <v>491</v>
+      </c>
+      <c r="H57" s="20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I57" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="K57" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="L57" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="M57" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="N57" s="19" t="s">
+        <v>493</v>
+      </c>
+      <c r="O57" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="P57" s="21"/>
+    </row>
+    <row r="58" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="18" t="s">
+        <v>494</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>495</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="D58" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="E58" s="19" t="s">
+        <v>496</v>
+      </c>
+      <c r="F58" s="19" t="s">
+        <v>497</v>
+      </c>
+      <c r="G58" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="H58" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="I58" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="K58" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="L58" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="M58" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="N58" s="19" t="s">
+        <v>500</v>
+      </c>
+      <c r="O58" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="P58" s="21"/>
     </row>
     <row r="59" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="15" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>468</v>
+        <v>502</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>75</v>
@@ -6810,10 +7161,10 @@
         <v>92</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>478</v>
+        <v>504</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>76</v>
@@ -6837,19 +7188,19 @@
         <v>76</v>
       </c>
       <c r="N59" s="4" t="s">
-        <v>490</v>
+        <v>505</v>
       </c>
       <c r="O59" s="4" t="s">
         <v>76</v>
       </c>
       <c r="P59" s="17"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="15" t="s">
-        <v>491</v>
+        <v>506</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>468</v>
+        <v>502</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>75</v>
@@ -6858,10 +7209,10 @@
         <v>92</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>492</v>
+        <v>507</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>493</v>
+        <v>508</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>76</v>
@@ -6885,31 +7236,31 @@
         <v>76</v>
       </c>
       <c r="N60" s="4" t="s">
-        <v>494</v>
+        <v>509</v>
       </c>
       <c r="O60" s="4" t="s">
         <v>76</v>
       </c>
       <c r="P60" s="17"/>
     </row>
-    <row r="61" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="15" t="s">
-        <v>495</v>
+        <v>510</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>76</v>
+        <v>502</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>92</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>496</v>
+        <v>511</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>497</v>
+        <v>512</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>76</v>
@@ -6921,7 +7272,7 @@
         <v>0</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K61" s="4" t="s">
         <v>76</v>
@@ -6933,16 +7284,304 @@
         <v>76</v>
       </c>
       <c r="N61" s="4" t="s">
-        <v>498</v>
+        <v>513</v>
       </c>
       <c r="O61" s="4" t="s">
         <v>76</v>
       </c>
       <c r="P61" s="17"/>
     </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="15" t="s">
+        <v>514</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>516</v>
+      </c>
+      <c r="G62" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L62" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="M62" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="N62" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="O62" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="P62" s="17"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="15" t="s">
+        <v>518</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E63" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="F63" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="G63" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L63" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="M63" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="N63" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="O63" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="P63" s="17"/>
+    </row>
+    <row r="64" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="15" t="s">
+        <v>522</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E64" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>512</v>
+      </c>
+      <c r="G64" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L64" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="M64" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="N64" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="O64" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="P64" s="17"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="15" t="s">
+        <v>525</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E65" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="G65" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L65" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="M65" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="N65" s="4" t="s">
+        <v>528</v>
+      </c>
+      <c r="O65" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="P65" s="17"/>
+    </row>
+    <row r="66" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="15" t="s">
+        <v>529</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="G66" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L66" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="M66" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="N66" s="4" t="s">
+        <v>532</v>
+      </c>
+      <c r="O66" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="P66" s="17"/>
+    </row>
+    <row r="67" customFormat="false" ht="109.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="18" t="s">
+        <v>533</v>
+      </c>
+      <c r="B67" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C67" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D67" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E67" s="19" t="s">
+        <v>534</v>
+      </c>
+      <c r="F67" s="19" t="s">
+        <v>535</v>
+      </c>
+      <c r="G67" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="H67" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="K67" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="L67" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="M67" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="N67" s="19" t="s">
+        <v>536</v>
+      </c>
+      <c r="O67" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="P67" s="21"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:P61"/>
-  <conditionalFormatting sqref="A2:P61">
+  <autoFilter ref="A1:P67"/>
+  <conditionalFormatting sqref="A2:P67">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>$O2="Xong"</formula>
     </cfRule>
@@ -6954,15 +7593,15 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C61" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C2:C67" type="list">
       <formula1>"P0,P1,P2,—"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J61" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="J2:J67" type="list">
       <formula1>"GĐ1 · T1–2 · 29/9–12/10,GĐ2 · T3–4 · 13/10–26/10,GĐ3 · T5–6 · 27/10–9/11,GĐ4 · T7–8 · 10/11–23/11,GĐ5 · T9–10 · 24/11–7/12,GĐ6 · T11–12 · 8/12–21/12,Sau MVP,Không làm (P2)"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="O2:O61" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="O2:O67" type="list">
       <formula1>"Chưa bắt đầu,Đang làm,Xong,Tắc,—"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -6983,7 +7622,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
@@ -6996,322 +7635,402 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>499</v>
+        <v>537</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>500</v>
+        <v>538</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>501</v>
+        <v>539</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>502</v>
+        <v>540</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>503</v>
+        <v>541</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>504</v>
+        <v>542</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
-        <v>505</v>
+        <v>543</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>506</v>
+        <v>544</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>507</v>
+        <v>545</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>508</v>
+        <v>546</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>509</v>
+        <v>547</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>510</v>
+        <v>548</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
-        <v>511</v>
+        <v>549</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>512</v>
+        <v>550</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>513</v>
+        <v>551</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>514</v>
+        <v>552</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>515</v>
+        <v>553</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>516</v>
+        <v>554</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
-        <v>517</v>
+        <v>555</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>518</v>
+        <v>556</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>519</v>
+        <v>557</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>520</v>
+        <v>558</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>178</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>521</v>
+        <v>559</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>522</v>
+        <v>560</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>523</v>
+        <v>561</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>524</v>
+        <v>562</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>525</v>
+        <v>563</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>207</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>526</v>
+        <v>564</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>527</v>
+        <v>565</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>528</v>
+        <v>566</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>529</v>
+        <v>567</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>530</v>
+        <v>568</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>526</v>
+        <v>564</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>532</v>
+        <v>570</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>533</v>
+        <v>571</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>534</v>
+        <v>572</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>535</v>
+        <v>573</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>536</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>537</v>
+        <v>575</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>538</v>
+        <v>576</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>539</v>
+        <v>577</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>540</v>
+        <v>578</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>541</v>
+        <v>579</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>542</v>
+        <v>580</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>543</v>
+        <v>581</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>544</v>
+        <v>582</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>545</v>
+        <v>583</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>546</v>
+        <v>584</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>547</v>
+        <v>585</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>526</v>
+        <v>564</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>548</v>
+        <v>586</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>549</v>
+        <v>587</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>550</v>
+        <v>588</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>551</v>
+        <v>589</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>552</v>
+        <v>590</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>526</v>
+        <v>564</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>553</v>
+        <v>591</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>554</v>
+        <v>592</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>555</v>
+        <v>593</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>556</v>
+        <v>594</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>557</v>
+        <v>595</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>558</v>
+        <v>596</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>559</v>
+        <v>597</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>560</v>
+        <v>598</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>561</v>
+        <v>599</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>562</v>
+        <v>600</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>126</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>563</v>
+        <v>601</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>564</v>
+        <v>602</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>565</v>
+        <v>603</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>566</v>
+        <v>604</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>567</v>
+        <v>605</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>568</v>
+        <v>606</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>569</v>
+        <v>607</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
+        <v>602</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>564</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>570</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
+        <v>602</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="F15" s="4" t="s">
         <v>564</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>574</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>577</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="18" t="s">
-        <v>578</v>
+        <v>616</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>579</v>
+        <v>617</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>580</v>
+        <v>618</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>581</v>
+        <v>619</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>582</v>
+        <v>620</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>583</v>
+        <v>621</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
+        <v>616</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>622</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>623</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>624</v>
+      </c>
+      <c r="E17" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
+        <v>616</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>626</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>627</v>
+      </c>
+      <c r="D18" s="19" t="s">
+        <v>628</v>
+      </c>
+      <c r="E18" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="F18" s="19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>616</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>629</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>630</v>
+      </c>
+      <c r="D19" s="19" t="s">
+        <v>631</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>632</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="57" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
+        <v>616</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>633</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>634</v>
+      </c>
+      <c r="D20" s="19" t="s">
+        <v>635</v>
+      </c>
+      <c r="E20" s="19" t="s">
+        <v>636</v>
+      </c>
+      <c r="F20" s="19" t="s">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -7326,6 +8045,371 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:K14"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>637</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>638</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>639</v>
+      </c>
+      <c r="D1" s="6" t="s">
+        <v>640</v>
+      </c>
+      <c r="E1" s="6" t="s">
+        <v>641</v>
+      </c>
+      <c r="F1" s="6" t="s">
+        <v>642</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>643</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" s="6" t="s">
+        <v>644</v>
+      </c>
+      <c r="J1" s="6" t="s">
+        <v>645</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>650</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>652</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>654</v>
+      </c>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+    </row>
+    <row r="3" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>663</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>653</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>664</v>
+      </c>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+    </row>
+    <row r="5" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>667</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>670</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+    </row>
+    <row r="6" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+    </row>
+    <row r="7" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>675</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+    </row>
+    <row r="9" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>680</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>683</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+    </row>
+    <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>686</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+    </row>
+    <row r="11" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>689</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+    </row>
+    <row r="12" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="22" t="s">
+        <v>696</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -7349,31 +8433,31 @@
         <v>105</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>584</v>
+        <v>697</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>585</v>
+        <v>698</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>586</v>
+        <v>699</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>587</v>
+        <v>700</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>588</v>
+        <v>701</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>589</v>
+        <v>702</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>196</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>464</v>
+        <v>484</v>
       </c>
       <c r="J1" s="6" t="s">
-        <v>590</v>
+        <v>703</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7381,16 +8465,16 @@
         <v>115</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>591</v>
+        <v>704</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>592</v>
+        <v>705</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>593</v>
+        <v>706</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>594</v>
+        <v>707</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>76</v>
@@ -7399,13 +8483,13 @@
         <v>76</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>595</v>
+        <v>708</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>596</v>
+        <v>709</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>597</v>
+        <v>710</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7413,16 +8497,16 @@
         <v>131</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>598</v>
+        <v>711</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>599</v>
+        <v>712</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>600</v>
+        <v>713</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>601</v>
+        <v>714</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>76</v>
@@ -7431,13 +8515,13 @@
         <v>76</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>602</v>
+        <v>715</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>603</v>
+        <v>716</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>604</v>
+        <v>717</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7445,153 +8529,153 @@
         <v>212</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>605</v>
+        <v>718</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>606</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>607</v>
+        <v>719</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>720</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>608</v>
+        <v>721</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>76</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>609</v>
+        <v>722</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>610</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>611</v>
+        <v>723</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>724</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>612</v>
+        <v>725</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
-        <v>613</v>
+        <v>726</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>614</v>
+        <v>727</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>615</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>616</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>617</v>
+        <v>728</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>729</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>730</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>76</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>618</v>
+        <v>731</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>619</v>
+        <v>732</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>620</v>
+        <v>733</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>621</v>
+        <v>734</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>622</v>
+        <v>735</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>623</v>
+        <v>736</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>624</v>
+        <v>737</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>625</v>
+        <v>738</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>626</v>
+        <v>739</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>627</v>
-      </c>
-      <c r="H6" s="19" t="s">
-        <v>628</v>
+        <v>740</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>741</v>
       </c>
       <c r="I6" s="4" t="s">
         <v>76</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>629</v>
+        <v>742</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>630</v>
+        <v>743</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>631</v>
+        <v>744</v>
       </c>
       <c r="D7" s="19" t="s">
-        <v>632</v>
+        <v>745</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>633</v>
+        <v>746</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>634</v>
+        <v>747</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>635</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>636</v>
+        <v>748</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>749</v>
       </c>
       <c r="I7" s="4" t="s">
         <v>76</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>629</v>
+        <v>742</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>637</v>
+        <v>750</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>638</v>
+        <v>751</v>
       </c>
       <c r="D8" s="19" t="s">
-        <v>639</v>
+        <v>752</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>640</v>
+        <v>753</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>641</v>
+        <v>754</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>642</v>
+        <v>755</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>643</v>
+        <v>756</v>
       </c>
       <c r="I8" s="4" t="s">
         <v>76</v>
@@ -7602,28 +8686,28 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
-        <v>325</v>
+        <v>339</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>644</v>
+        <v>757</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>645</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>646</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>647</v>
+        <v>758</v>
+      </c>
+      <c r="D9" s="19" t="s">
+        <v>759</v>
+      </c>
+      <c r="E9" s="19" t="s">
+        <v>760</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>648</v>
+        <v>761</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>649</v>
+        <v>762</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>650</v>
+        <v>763</v>
       </c>
       <c r="I9" s="4" t="s">
         <v>76</v>
@@ -7634,31 +8718,31 @@
     </row>
     <row r="10" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
-        <v>339</v>
+        <v>359</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>651</v>
+        <v>764</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>652</v>
+        <v>765</v>
       </c>
       <c r="D10" s="19" t="s">
-        <v>653</v>
+        <v>766</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>654</v>
+        <v>767</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>655</v>
+        <v>768</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>656</v>
+        <v>769</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>657</v>
+        <v>770</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>658</v>
+        <v>771</v>
       </c>
       <c r="J10" s="4" t="s">
         <v>76</v>
@@ -7666,63 +8750,63 @@
     </row>
     <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>659</v>
+        <v>772</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>660</v>
+        <v>773</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>661</v>
+        <v>774</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>662</v>
+        <v>775</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>76</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>663</v>
+        <v>776</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>657</v>
+        <v>770</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>664</v>
+        <v>777</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>665</v>
+        <v>778</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
-        <v>415</v>
+        <v>435</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>666</v>
+        <v>779</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>667</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>668</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>669</v>
+        <v>780</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>781</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>782</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>76</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>670</v>
+        <v>783</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="I12" s="4" t="s">
-        <v>671</v>
+      <c r="I12" s="19" t="s">
+        <v>784</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>76</v>
@@ -7730,34 +8814,34 @@
     </row>
     <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>672</v>
+        <v>785</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>673</v>
+        <v>786</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>674</v>
+        <v>787</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>675</v>
+        <v>788</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>76</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>676</v>
+        <v>789</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>76</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>677</v>
+        <v>790</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>678</v>
+        <v>791</v>
       </c>
     </row>
   </sheetData>
